--- a/data/transactions/_unit-mismatches/unit-mismatches.xlsx
+++ b/data/transactions/_unit-mismatches/unit-mismatches.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="38">
   <si>
     <t>الكود</t>
   </si>
@@ -31,30 +31,15 @@
     <t>آخر رقم فاتورة</t>
   </si>
   <si>
-    <t>10106020</t>
-  </si>
-  <si>
-    <t>لفة ماسورة نحاس 4/1</t>
-  </si>
-  <si>
-    <t>متر</t>
+    <t>10106040</t>
+  </si>
+  <si>
+    <t>فريون 1ك R134</t>
   </si>
   <si>
     <t>عدد</t>
   </si>
   <si>
-    <t>اسكيمو للهندسه، الفاروق</t>
-  </si>
-  <si>
-    <t>2461</t>
-  </si>
-  <si>
-    <t>10106040</t>
-  </si>
-  <si>
-    <t>فريون 1ك R134</t>
-  </si>
-  <si>
     <t>كيلو</t>
   </si>
   <si>
@@ -64,105 +49,6 @@
     <t>2437</t>
   </si>
   <si>
-    <t>10207003</t>
-  </si>
-  <si>
-    <t>كابل ترموبلاستيك 3×4مم سويدى</t>
-  </si>
-  <si>
-    <t>متر، لفة</t>
-  </si>
-  <si>
-    <t>نيو المصريه</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>10207005</t>
-  </si>
-  <si>
-    <t>كابل ترموبلاستيك 4×6مم سويدى</t>
-  </si>
-  <si>
-    <t>االعصريه</t>
-  </si>
-  <si>
-    <t>929</t>
-  </si>
-  <si>
-    <t>10207013</t>
-  </si>
-  <si>
-    <t>سلك حرارى 1 مم ايطالى</t>
-  </si>
-  <si>
-    <t>االعصريه، العصريه</t>
-  </si>
-  <si>
-    <t>1031</t>
-  </si>
-  <si>
-    <t>10207014</t>
-  </si>
-  <si>
-    <t>سلك حرارى 2 مم ايطالى</t>
-  </si>
-  <si>
-    <t>10207015</t>
-  </si>
-  <si>
-    <t>سلك حرارى 4 مم ايطالى</t>
-  </si>
-  <si>
-    <t>10209001</t>
-  </si>
-  <si>
-    <t>عود مكرونه حرارى 8 مم</t>
-  </si>
-  <si>
-    <t>ايجل</t>
-  </si>
-  <si>
-    <t>10889</t>
-  </si>
-  <si>
-    <t>10209047</t>
-  </si>
-  <si>
-    <t>فلكسبل حرارى 25مم</t>
-  </si>
-  <si>
-    <t>928</t>
-  </si>
-  <si>
-    <t>10209048</t>
-  </si>
-  <si>
-    <t>فلكيسيبل حرارى 32 مم ايطالى</t>
-  </si>
-  <si>
-    <t>10308021</t>
-  </si>
-  <si>
-    <t>خرطوم غاز 8 مم 20 بار ايطالى</t>
-  </si>
-  <si>
-    <t>المصطفي</t>
-  </si>
-  <si>
-    <t>4905</t>
-  </si>
-  <si>
-    <t>10501017</t>
-  </si>
-  <si>
-    <t>لفه جوان حراري احمر</t>
-  </si>
-  <si>
-    <t>10994</t>
-  </si>
-  <si>
     <t>10801007</t>
   </si>
   <si>
@@ -179,18 +65,6 @@
   </si>
   <si>
     <t>783</t>
-  </si>
-  <si>
-    <t>11009026</t>
-  </si>
-  <si>
-    <t>سلسلة حديد 4 مم</t>
-  </si>
-  <si>
-    <t>العزم</t>
-  </si>
-  <si>
-    <t>11515</t>
   </si>
   <si>
     <t>11301010</t>
@@ -680,7 +554,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -739,56 +613,56 @@
         <v>13</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>24</v>
-      </c>
       <c r="F5" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -799,340 +673,100 @@
         <v>27</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F22"/>
+  <autoFilter ref="A1:F10"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>

--- a/data/transactions/_unit-mismatches/unit-mismatches.xlsx
+++ b/data/transactions/_unit-mismatches/unit-mismatches.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>الكود</t>
   </si>
@@ -29,109 +29,13 @@
   </si>
   <si>
     <t>آخر رقم فاتورة</t>
-  </si>
-  <si>
-    <t>10106040</t>
-  </si>
-  <si>
-    <t>فريون 1ك R134</t>
-  </si>
-  <si>
-    <t>عدد</t>
-  </si>
-  <si>
-    <t>كيلو</t>
-  </si>
-  <si>
-    <t>الفاروق</t>
-  </si>
-  <si>
-    <t>2437</t>
-  </si>
-  <si>
-    <t>10801007</t>
-  </si>
-  <si>
-    <t>خشب شوايه فلندي 3/4 ×4</t>
-  </si>
-  <si>
-    <t>متر³</t>
-  </si>
-  <si>
-    <t>متر 2</t>
-  </si>
-  <si>
-    <t>اخشاب النعام</t>
-  </si>
-  <si>
-    <t>783</t>
-  </si>
-  <si>
-    <t>11301010</t>
-  </si>
-  <si>
-    <t>لوح 1.2 مم SST مط مغلف 1.25 × 2.5 م</t>
-  </si>
-  <si>
-    <t>عدد، كيلوجرام، طن</t>
-  </si>
-  <si>
-    <t>(فارغ)</t>
-  </si>
-  <si>
-    <t>المصريه لتشكيل المعادن</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>11301012</t>
-  </si>
-  <si>
-    <t>لوح 1.5 مم SST مط مغلف 1 × 2 م</t>
-  </si>
-  <si>
-    <t>11301021</t>
-  </si>
-  <si>
-    <t>لوح 0.8 مم SST مصنفر مغلف 1.25 ×2 م</t>
-  </si>
-  <si>
-    <t>11301026</t>
-  </si>
-  <si>
-    <t>لوح 1.25 مم SST مصنفر مغلف 1 × 2 م</t>
-  </si>
-  <si>
-    <t>11301030</t>
-  </si>
-  <si>
-    <t>لوح 1.5 مم SST مصنفر مغلف 1.25 × 2.5 م</t>
-  </si>
-  <si>
-    <t>11301049</t>
-  </si>
-  <si>
-    <t>لوح 2 مم SST مصنفر مغلف 1.25 × 2 م</t>
-  </si>
-  <si>
-    <t>11407006</t>
-  </si>
-  <si>
-    <t>لوح صاج 2 مم اسود - مقاس 1×2م</t>
-  </si>
-  <si>
-    <t>الاسراء</t>
-  </si>
-  <si>
-    <t>705</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -145,12 +49,8 @@
       <sz val="12"/>
       <name val="Arial"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -160,11 +60,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1E3A5F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F5F9"/>
       </patternFill>
     </fill>
   </fills>
@@ -195,22 +90,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -554,7 +437,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -585,188 +468,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F10"/>
+  <autoFilter ref="A1:F1"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>

--- a/data/transactions/_unit-mismatches/unit-mismatches.xlsx
+++ b/data/transactions/_unit-mismatches/unit-mismatches.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
     <t>الكود</t>
   </si>
@@ -29,13 +29,70 @@
   </si>
   <si>
     <t>آخر رقم فاتورة</t>
+  </si>
+  <si>
+    <t>اسم الملف</t>
+  </si>
+  <si>
+    <t>10106040</t>
+  </si>
+  <si>
+    <t>فريون 1ك R134</t>
+  </si>
+  <si>
+    <t>عدد</t>
+  </si>
+  <si>
+    <t>كيلو</t>
+  </si>
+  <si>
+    <t>الفاروق</t>
+  </si>
+  <si>
+    <t>2437</t>
+  </si>
+  <si>
+    <t>أذونات الإضافة لشهر 3.xlsx</t>
+  </si>
+  <si>
+    <t>10801007</t>
+  </si>
+  <si>
+    <t>خشب شوايه فلندي 3/4 ×4</t>
+  </si>
+  <si>
+    <t>متر³</t>
+  </si>
+  <si>
+    <t>متر 2</t>
+  </si>
+  <si>
+    <t>اخشاب النعام</t>
+  </si>
+  <si>
+    <t>783</t>
+  </si>
+  <si>
+    <t>11404002</t>
+  </si>
+  <si>
+    <t>خوصة حديد 20 × 40 مم × 6 م</t>
+  </si>
+  <si>
+    <t>الاسراء</t>
+  </si>
+  <si>
+    <t>709</t>
+  </si>
+  <si>
+    <t>أذونات الإضافة لشهر 6.xlsx</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -49,8 +106,12 @@
       <sz val="12"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -60,6 +121,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1E3A5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F5F9"/>
       </patternFill>
     </fill>
   </fills>
@@ -90,10 +156,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -437,7 +515,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -446,9 +524,10 @@
     <col min="4" max="4" width="22" customWidth="1"/>
     <col min="5" max="5" width="40" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -467,9 +546,81 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>24</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:G4"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>

--- a/data/transactions/_unit-mismatches/unit-mismatches.xlsx
+++ b/data/transactions/_unit-mismatches/unit-mismatches.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>الكود</t>
   </si>
@@ -71,21 +71,6 @@
   </si>
   <si>
     <t>783</t>
-  </si>
-  <si>
-    <t>11404002</t>
-  </si>
-  <si>
-    <t>خوصة حديد 20 × 40 مم × 6 م</t>
-  </si>
-  <si>
-    <t>الاسراء</t>
-  </si>
-  <si>
-    <t>709</t>
-  </si>
-  <si>
-    <t>أذونات الإضافة لشهر 6.xlsx</t>
   </si>
 </sst>
 </file>
@@ -515,7 +500,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -596,31 +581,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G3"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>

--- a/data/transactions/_unit-mismatches/unit-mismatches.xlsx
+++ b/data/transactions/_unit-mismatches/unit-mismatches.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>الكود</t>
   </si>
@@ -32,52 +32,13 @@
   </si>
   <si>
     <t>اسم الملف</t>
-  </si>
-  <si>
-    <t>10106040</t>
-  </si>
-  <si>
-    <t>فريون 1ك R134</t>
-  </si>
-  <si>
-    <t>عدد</t>
-  </si>
-  <si>
-    <t>كيلو</t>
-  </si>
-  <si>
-    <t>الفاروق</t>
-  </si>
-  <si>
-    <t>2437</t>
-  </si>
-  <si>
-    <t>أذونات الإضافة لشهر 3.xlsx</t>
-  </si>
-  <si>
-    <t>10801007</t>
-  </si>
-  <si>
-    <t>خشب شوايه فلندي 3/4 ×4</t>
-  </si>
-  <si>
-    <t>متر³</t>
-  </si>
-  <si>
-    <t>متر 2</t>
-  </si>
-  <si>
-    <t>اخشاب النعام</t>
-  </si>
-  <si>
-    <t>783</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -91,12 +52,8 @@
       <sz val="12"/>
       <name val="Arial"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -106,11 +63,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1E3A5F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F5F9"/>
       </patternFill>
     </fill>
   </fills>
@@ -141,22 +93,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -500,7 +440,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -535,54 +475,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G1"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
